--- a/2022 data/excel_outputs/158_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/158_boothwise_data.xlsx
@@ -14,11 +14,83 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="443">
   <si>
     <t>AC 158 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -322,7 +394,7 @@
     <t>P P DURGAGANJ ROOM 1</t>
   </si>
   <si>
-    <t>P P DURGAGANJ ROOM ■</t>
+    <t>CHNCHANCHAMTAMNABIP</t>
   </si>
   <si>
     <t>P P SARAUNA</t>
@@ -1114,7 +1186,7 @@
     <t>J H S BEEKAPUR ROOM NO.1</t>
   </si>
   <si>
-    <t>J H S BEEKAPUR ROOM NO.■</t>
+    <t>J H S BEEKAPUR ROOM ROOM NO. 364</t>
   </si>
   <si>
     <t>J H S BEEKAPUR EXTRA ROOM</t>
@@ -1277,8 +1349,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1294,7 +1374,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1302,12 +1382,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1606,85 +1704,157 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="D2" t="s">
-        <v>397</v>
+        <v>421</v>
       </c>
       <c r="E2" t="s">
-        <v>398</v>
+        <v>422</v>
       </c>
       <c r="F2" t="s">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="G2" t="s">
-        <v>400</v>
+        <v>424</v>
       </c>
       <c r="H2" t="s">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="I2" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="J2" t="s">
-        <v>403</v>
+        <v>427</v>
       </c>
       <c r="K2" t="s">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="L2" t="s">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="M2" t="s">
-        <v>406</v>
+        <v>430</v>
       </c>
       <c r="N2" t="s">
-        <v>407</v>
+        <v>431</v>
       </c>
       <c r="O2" t="s">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="P2" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="Q2" t="s">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="R2" t="s">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="S2" t="s">
-        <v>412</v>
+        <v>436</v>
       </c>
       <c r="T2" t="s">
-        <v>413</v>
+        <v>437</v>
       </c>
       <c r="U2" t="s">
-        <v>414</v>
+        <v>438</v>
       </c>
       <c r="V2" t="s">
-        <v>415</v>
+        <v>439</v>
       </c>
       <c r="W2" t="s">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="X2" t="s">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="Y2" t="s">
-        <v>418</v>
+        <v>442</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1692,7 +1862,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1769,7 +1939,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1846,7 +2016,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1923,7 +2093,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -2000,7 +2170,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -2077,7 +2247,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -2154,7 +2324,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -2231,7 +2401,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -2308,7 +2478,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -2385,7 +2555,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -2462,7 +2632,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -2539,7 +2709,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -2616,7 +2786,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -2693,7 +2863,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -2770,7 +2940,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -2847,7 +3017,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -2924,7 +3094,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -3001,7 +3171,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -3078,7 +3248,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -3155,7 +3325,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -3232,7 +3402,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -3309,7 +3479,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -3386,7 +3556,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -3463,7 +3633,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -3540,7 +3710,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -3617,7 +3787,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -3694,7 +3864,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -3771,7 +3941,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -3848,7 +4018,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -3925,7 +4095,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -4002,7 +4172,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -4079,7 +4249,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -4156,7 +4326,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -4233,7 +4403,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -4310,7 +4480,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -4387,7 +4557,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -4464,7 +4634,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -4541,7 +4711,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -4618,7 +4788,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -4695,7 +4865,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -4772,7 +4942,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -4849,7 +5019,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -4926,7 +5096,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -5003,7 +5173,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -5080,7 +5250,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -5157,7 +5327,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -5234,7 +5404,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -5311,7 +5481,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -5388,7 +5558,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -5465,7 +5635,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -5542,7 +5712,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -5619,7 +5789,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -5696,7 +5866,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -5773,7 +5943,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -5850,7 +6020,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -5927,7 +6097,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -6004,7 +6174,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -6081,7 +6251,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -6158,7 +6328,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -6235,7 +6405,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -6312,7 +6482,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -6389,7 +6559,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -6466,7 +6636,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -6543,7 +6713,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -6620,7 +6790,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -6697,7 +6867,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -6774,7 +6944,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -6851,7 +7021,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -6928,7 +7098,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -7005,7 +7175,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -7082,7 +7252,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -7159,7 +7329,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -7236,7 +7406,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -7313,7 +7483,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -7390,7 +7560,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -7467,7 +7637,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -7544,7 +7714,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -7621,7 +7791,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -7698,7 +7868,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -7775,7 +7945,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -7852,7 +8022,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -7929,7 +8099,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -8006,7 +8176,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -8083,7 +8253,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -8160,7 +8330,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -8237,7 +8407,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -8314,7 +8484,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -8391,7 +8561,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -8468,7 +8638,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -8545,7 +8715,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -8622,7 +8792,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -8699,7 +8869,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -8776,7 +8946,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -8853,7 +9023,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -8930,7 +9100,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -9007,7 +9177,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -9084,7 +9254,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -9161,7 +9331,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -9238,7 +9408,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -9315,7 +9485,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -9392,7 +9562,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -9469,7 +9639,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -9546,7 +9716,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -9623,7 +9793,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -9700,7 +9870,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -9777,7 +9947,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -9854,7 +10024,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -9931,7 +10101,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -10008,7 +10178,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -10085,7 +10255,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -10162,7 +10332,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -10239,7 +10409,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -10316,7 +10486,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -10393,7 +10563,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -10470,7 +10640,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -10547,7 +10717,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -10624,7 +10794,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -10701,7 +10871,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -10778,7 +10948,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -10855,7 +11025,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -10932,7 +11102,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -11009,7 +11179,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -11086,7 +11256,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -11163,7 +11333,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -11240,7 +11410,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -11317,7 +11487,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -11394,7 +11564,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -11471,7 +11641,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -11548,7 +11718,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -11625,7 +11795,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -11702,7 +11872,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -11779,7 +11949,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -11856,7 +12026,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -11933,7 +12103,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -12010,7 +12180,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -12087,7 +12257,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -12164,7 +12334,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -12241,7 +12411,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -12318,7 +12488,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -12395,7 +12565,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -12472,7 +12642,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -12549,7 +12719,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -12626,7 +12796,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -12703,7 +12873,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -12780,7 +12950,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -12857,7 +13027,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -12934,7 +13104,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -13011,7 +13181,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -13088,7 +13258,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -13165,7 +13335,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -13242,7 +13412,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -13319,7 +13489,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -13396,7 +13566,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -13473,7 +13643,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -13550,7 +13720,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -13627,7 +13797,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -13704,7 +13874,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -13781,7 +13951,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -13858,7 +14028,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -13935,7 +14105,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -14012,7 +14182,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -14089,7 +14259,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -14166,7 +14336,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -14243,7 +14413,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -14320,7 +14490,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -14397,7 +14567,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -14474,7 +14644,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -14551,7 +14721,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -14628,7 +14798,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -14705,7 +14875,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -14782,7 +14952,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -14859,7 +15029,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -14936,7 +15106,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -15013,7 +15183,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -15090,7 +15260,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -15167,7 +15337,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -15244,7 +15414,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -15321,7 +15491,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -15398,7 +15568,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -15475,7 +15645,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -15552,7 +15722,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -15629,7 +15799,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -15706,7 +15876,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -15783,7 +15953,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -15860,7 +16030,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -15937,7 +16107,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -16014,7 +16184,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -16091,7 +16261,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -16168,7 +16338,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -16245,7 +16415,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -16322,7 +16492,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -16399,7 +16569,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="C194">
         <v>0</v>
@@ -16476,7 +16646,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -16553,7 +16723,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -16630,7 +16800,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -16707,7 +16877,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -16784,7 +16954,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -16861,7 +17031,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -16938,7 +17108,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -17015,7 +17185,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -17092,7 +17262,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -17169,7 +17339,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -17246,7 +17416,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -17323,7 +17493,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -17400,7 +17570,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -17477,7 +17647,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -17554,7 +17724,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -17631,7 +17801,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -17708,7 +17878,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -17785,7 +17955,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="C212">
         <v>0</v>
@@ -17862,7 +18032,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -17939,7 +18109,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -18016,7 +18186,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>215</v>
+        <v>239</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -18093,7 +18263,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -18170,7 +18340,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="C217">
         <v>0</v>
@@ -18247,7 +18417,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="C218">
         <v>0</v>
@@ -18324,7 +18494,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="C219">
         <v>0</v>
@@ -18401,7 +18571,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -18478,7 +18648,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="C221">
         <v>0</v>
@@ -18555,7 +18725,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="C222">
         <v>0</v>
@@ -18632,7 +18802,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="C223">
         <v>0</v>
@@ -18709,7 +18879,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="C224">
         <v>0</v>
@@ -18786,7 +18956,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -18863,7 +19033,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -18940,7 +19110,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -19017,7 +19187,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="C228">
         <v>0</v>
@@ -19094,7 +19264,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="C229">
         <v>0</v>
@@ -19171,7 +19341,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="C230">
         <v>0</v>
@@ -19248,7 +19418,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="C231">
         <v>0</v>
@@ -19325,7 +19495,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="C232">
         <v>0</v>
@@ -19402,7 +19572,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="C233">
         <v>0</v>
@@ -19479,7 +19649,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="C234">
         <v>0</v>
@@ -19556,7 +19726,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="C235">
         <v>0</v>
@@ -19633,7 +19803,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -19710,7 +19880,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -19787,7 +19957,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -19864,7 +20034,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="C239">
         <v>0</v>
@@ -19941,7 +20111,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="C240">
         <v>0</v>
@@ -20018,7 +20188,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="C241">
         <v>0</v>
@@ -20095,7 +20265,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="C242">
         <v>0</v>
@@ -20172,7 +20342,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="C243">
         <v>0</v>
@@ -20249,7 +20419,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="C244">
         <v>0</v>
@@ -20326,7 +20496,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="C245">
         <v>0</v>
@@ -20403,7 +20573,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -20480,7 +20650,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="C247">
         <v>0</v>
@@ -20557,7 +20727,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="C248">
         <v>0</v>
@@ -20634,7 +20804,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="C249">
         <v>0</v>
@@ -20711,7 +20881,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="C250">
         <v>0</v>
@@ -20788,7 +20958,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="C251">
         <v>0</v>
@@ -20865,7 +21035,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="C252">
         <v>0</v>
@@ -20942,7 +21112,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="C253">
         <v>0</v>
@@ -21019,7 +21189,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="C254">
         <v>0</v>
@@ -21096,7 +21266,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="C255">
         <v>0</v>
@@ -21173,7 +21343,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="C256">
         <v>0</v>
@@ -21250,7 +21420,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="C257">
         <v>0</v>
@@ -21327,7 +21497,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="C258">
         <v>0</v>
@@ -21404,7 +21574,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="C259">
         <v>0</v>
@@ -21481,7 +21651,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="C260">
         <v>0</v>
@@ -21558,7 +21728,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="C261">
         <v>0</v>
@@ -21635,7 +21805,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="C262">
         <v>0</v>
@@ -21712,7 +21882,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="C263">
         <v>0</v>
@@ -21789,7 +21959,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="C264">
         <v>0</v>
@@ -21866,7 +22036,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="C265">
         <v>0</v>
@@ -21943,7 +22113,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="C266">
         <v>0</v>
@@ -22020,7 +22190,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="C267">
         <v>0</v>
@@ -22097,7 +22267,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="C268">
         <v>0</v>
@@ -22174,7 +22344,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="C269">
         <v>0</v>
@@ -22251,7 +22421,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="C270">
         <v>0</v>
@@ -22328,7 +22498,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="C271">
         <v>0</v>
@@ -22405,7 +22575,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="C272">
         <v>0</v>
@@ -22482,7 +22652,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="C273">
         <v>0</v>
@@ -22559,7 +22729,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="C274">
         <v>0</v>
@@ -22636,7 +22806,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="C275">
         <v>0</v>
@@ -22713,7 +22883,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="C276">
         <v>0</v>
@@ -22790,7 +22960,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="C277">
         <v>0</v>
@@ -22867,7 +23037,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="C278">
         <v>0</v>
@@ -22944,7 +23114,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="C279">
         <v>0</v>
@@ -23021,7 +23191,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="C280">
         <v>0</v>
@@ -23098,7 +23268,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="C281">
         <v>0</v>
@@ -23175,7 +23345,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>282</v>
+        <v>306</v>
       </c>
       <c r="C282">
         <v>0</v>
@@ -23252,7 +23422,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="C283">
         <v>0</v>
@@ -23329,7 +23499,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="C284">
         <v>0</v>
@@ -23406,7 +23576,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="C285">
         <v>0</v>
@@ -23483,7 +23653,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="C286">
         <v>0</v>
@@ -23560,7 +23730,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="C287">
         <v>0</v>
@@ -23637,7 +23807,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="C288">
         <v>0</v>
@@ -23714,7 +23884,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>289</v>
+        <v>313</v>
       </c>
       <c r="C289">
         <v>0</v>
@@ -23791,7 +23961,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>290</v>
+        <v>314</v>
       </c>
       <c r="C290">
         <v>0</v>
@@ -23868,7 +24038,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="C291">
         <v>0</v>
@@ -23945,7 +24115,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="C292">
         <v>0</v>
@@ -24022,7 +24192,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="C293">
         <v>0</v>
@@ -24099,7 +24269,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>294</v>
+        <v>318</v>
       </c>
       <c r="C294">
         <v>0</v>
@@ -24176,7 +24346,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="C295">
         <v>0</v>
@@ -24253,7 +24423,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="C296">
         <v>0</v>
@@ -24330,7 +24500,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>297</v>
+        <v>321</v>
       </c>
       <c r="C297">
         <v>0</v>
@@ -24407,7 +24577,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="C298">
         <v>0</v>
@@ -24484,7 +24654,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>299</v>
+        <v>323</v>
       </c>
       <c r="C299">
         <v>0</v>
@@ -24561,7 +24731,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>300</v>
+        <v>324</v>
       </c>
       <c r="C300">
         <v>0</v>
@@ -24638,7 +24808,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="C301">
         <v>0</v>
@@ -24715,7 +24885,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="C302">
         <v>0</v>
@@ -24792,7 +24962,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>303</v>
+        <v>327</v>
       </c>
       <c r="C303">
         <v>0</v>
@@ -24869,7 +25039,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>304</v>
+        <v>328</v>
       </c>
       <c r="C304">
         <v>0</v>
@@ -24946,7 +25116,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>305</v>
+        <v>329</v>
       </c>
       <c r="C305">
         <v>0</v>
@@ -25023,7 +25193,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="C306">
         <v>0</v>
@@ -25100,7 +25270,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="C307">
         <v>0</v>
@@ -25177,7 +25347,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>308</v>
+        <v>332</v>
       </c>
       <c r="C308">
         <v>0</v>
@@ -25254,7 +25424,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>309</v>
+        <v>333</v>
       </c>
       <c r="C309">
         <v>0</v>
@@ -25331,7 +25501,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="C310">
         <v>0</v>
@@ -25408,7 +25578,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="C311">
         <v>0</v>
@@ -25485,7 +25655,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>312</v>
+        <v>336</v>
       </c>
       <c r="C312">
         <v>0</v>
@@ -25562,7 +25732,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="C313">
         <v>0</v>
@@ -25639,7 +25809,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="C314">
         <v>0</v>
@@ -25716,7 +25886,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>315</v>
+        <v>339</v>
       </c>
       <c r="C315">
         <v>0</v>
@@ -25793,7 +25963,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="C316">
         <v>0</v>
@@ -25870,7 +26040,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="C317">
         <v>0</v>
@@ -25947,7 +26117,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="C318">
         <v>0</v>
@@ -26024,7 +26194,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>319</v>
+        <v>343</v>
       </c>
       <c r="C319">
         <v>0</v>
@@ -26101,7 +26271,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>320</v>
+        <v>344</v>
       </c>
       <c r="C320">
         <v>0</v>
@@ -26178,7 +26348,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="C321">
         <v>0</v>
@@ -26255,7 +26425,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="C322">
         <v>0</v>
@@ -26332,7 +26502,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>323</v>
+        <v>347</v>
       </c>
       <c r="C323">
         <v>0</v>
@@ -26409,7 +26579,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="C324">
         <v>0</v>
@@ -26486,7 +26656,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>325</v>
+        <v>349</v>
       </c>
       <c r="C325">
         <v>0</v>
@@ -26563,7 +26733,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>326</v>
+        <v>350</v>
       </c>
       <c r="C326">
         <v>0</v>
@@ -26640,7 +26810,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="C327">
         <v>0</v>
@@ -26717,7 +26887,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>328</v>
+        <v>352</v>
       </c>
       <c r="C328">
         <v>0</v>
@@ -26794,7 +26964,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>329</v>
+        <v>353</v>
       </c>
       <c r="C329">
         <v>0</v>
@@ -26871,7 +27041,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>330</v>
+        <v>354</v>
       </c>
       <c r="C330">
         <v>0</v>
@@ -26948,7 +27118,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="C331">
         <v>0</v>
@@ -27025,7 +27195,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="C332">
         <v>0</v>
@@ -27102,7 +27272,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="C333">
         <v>0</v>
@@ -27179,7 +27349,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>334</v>
+        <v>358</v>
       </c>
       <c r="C334">
         <v>0</v>
@@ -27256,7 +27426,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>335</v>
+        <v>359</v>
       </c>
       <c r="C335">
         <v>0</v>
@@ -27333,7 +27503,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>336</v>
+        <v>360</v>
       </c>
       <c r="C336">
         <v>0</v>
@@ -27410,7 +27580,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="C337">
         <v>0</v>
@@ -27487,7 +27657,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="C338">
         <v>0</v>
@@ -27564,7 +27734,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="C339">
         <v>0</v>
@@ -27641,7 +27811,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="C340">
         <v>0</v>
@@ -27718,7 +27888,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="C341">
         <v>0</v>
@@ -27795,7 +27965,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="C342">
         <v>0</v>
@@ -27872,7 +28042,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="C343">
         <v>0</v>
@@ -27949,7 +28119,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>344</v>
+        <v>368</v>
       </c>
       <c r="C344">
         <v>0</v>
@@ -28026,7 +28196,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="C345">
         <v>0</v>
@@ -28103,7 +28273,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="C346">
         <v>0</v>
@@ -28180,7 +28350,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>347</v>
+        <v>371</v>
       </c>
       <c r="C347">
         <v>0</v>
@@ -28257,7 +28427,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>348</v>
+        <v>372</v>
       </c>
       <c r="C348">
         <v>0</v>
@@ -28334,7 +28504,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>349</v>
+        <v>373</v>
       </c>
       <c r="C349">
         <v>0</v>
@@ -28411,7 +28581,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="C350">
         <v>0</v>
@@ -28488,7 +28658,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
       <c r="C351">
         <v>0</v>
@@ -28565,7 +28735,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="C352">
         <v>0</v>
@@ -28642,7 +28812,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="C353">
         <v>0</v>
@@ -28719,7 +28889,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>354</v>
+        <v>378</v>
       </c>
       <c r="C354">
         <v>0</v>
@@ -28796,7 +28966,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="C355">
         <v>0</v>
@@ -28873,7 +29043,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="C356">
         <v>0</v>
@@ -28950,7 +29120,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="C357">
         <v>0</v>
@@ -29027,7 +29197,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="C358">
         <v>0</v>
@@ -29104,7 +29274,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="C359">
         <v>0</v>
@@ -29181,7 +29351,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="C360">
         <v>0</v>
@@ -29258,7 +29428,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="C361">
         <v>0</v>
@@ -29335,7 +29505,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="C362">
         <v>0</v>
@@ -29412,7 +29582,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="C363">
         <v>0</v>
@@ -29489,7 +29659,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="C364">
         <v>0</v>
@@ -29566,7 +29736,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="C365">
         <v>0</v>
@@ -29643,7 +29813,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="C366">
         <v>0</v>
@@ -29720,7 +29890,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="C367">
         <v>0</v>
@@ -29797,7 +29967,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="C368">
         <v>0</v>
@@ -29874,7 +30044,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="C369">
         <v>0</v>
@@ -29951,7 +30121,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>370</v>
+        <v>394</v>
       </c>
       <c r="C370">
         <v>0</v>
@@ -30028,7 +30198,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="C371">
         <v>0</v>
@@ -30105,7 +30275,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="C372">
         <v>0</v>
@@ -30182,7 +30352,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="C373">
         <v>0</v>
@@ -30259,7 +30429,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>374</v>
+        <v>398</v>
       </c>
       <c r="C374">
         <v>0</v>
@@ -30336,7 +30506,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="C375">
         <v>0</v>
@@ -30413,7 +30583,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="C376">
         <v>0</v>
@@ -30490,7 +30660,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>377</v>
+        <v>401</v>
       </c>
       <c r="C377">
         <v>0</v>
@@ -30567,7 +30737,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="C378">
         <v>0</v>
@@ -30644,7 +30814,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="C379">
         <v>0</v>
@@ -30721,7 +30891,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="C380">
         <v>0</v>
@@ -30798,7 +30968,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="C381">
         <v>0</v>
@@ -30875,7 +31045,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="C382">
         <v>0</v>
@@ -30952,7 +31122,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="C383">
         <v>0</v>
@@ -31029,7 +31199,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="C384">
         <v>0</v>
@@ -31106,7 +31276,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="C385">
         <v>0</v>
@@ -31183,7 +31353,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="C386">
         <v>0</v>
@@ -31260,7 +31430,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="C387">
         <v>0</v>
@@ -31337,7 +31507,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="C388">
         <v>0</v>
@@ -31414,7 +31584,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="C389">
         <v>0</v>
@@ -31491,7 +31661,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="C390">
         <v>0</v>
@@ -31568,7 +31738,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>391</v>
+        <v>415</v>
       </c>
       <c r="C391">
         <v>0</v>
@@ -31645,7 +31815,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="C392">
         <v>0</v>
@@ -31722,7 +31892,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="C393">
         <v>0</v>
@@ -31799,7 +31969,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="C394">
         <v>0</v>
@@ -31876,7 +32046,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="C395">
         <v>0</v>
